--- a/results/02_taxa_assemblage/MRT_Method/ModelA_CoreOnly/tables/site_eval_train.xlsx
+++ b/results/02_taxa_assemblage/MRT_Method/ModelA_CoreOnly/tables/site_eval_train.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O36"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,20 +486,15 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Prob_Cluster 3</t>
+          <t>p_max</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>p_max</t>
+          <t>delta_p</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>delta_p</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
@@ -512,7 +507,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -520,7 +515,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>3.2004</v>
@@ -538,21 +533,18 @@
         <v>0.78</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3571428571428572</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1428571428571428</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="O2" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -597,15 +589,12 @@
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
         <v>1</v>
       </c>
-      <c r="N3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -614,11 +603,11 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>011A</t>
+          <t>030ABC</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -626,39 +615,36 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>6.2484</v>
+        <v>11.8872</v>
       </c>
       <c r="F4" t="n">
-        <v>8.550000000000001</v>
+        <v>9.18</v>
       </c>
       <c r="G4" t="n">
-        <v>21.96</v>
+        <v>16.66</v>
       </c>
       <c r="H4" t="n">
-        <v>1.580246913580247</v>
+        <v>0.918918918918919</v>
       </c>
       <c r="I4" t="n">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O4" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -667,7 +653,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>026C</t>
+          <t>035C</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -682,19 +668,19 @@
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>8.9916</v>
+        <v>12.4968</v>
       </c>
       <c r="F5" t="n">
-        <v>6.88</v>
+        <v>7.39</v>
       </c>
       <c r="G5" t="n">
-        <v>19.68</v>
+        <v>18.99</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3125</v>
+        <v>-1</v>
       </c>
       <c r="I5" t="n">
-        <v>1.795</v>
+        <v>3.99</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -703,15 +689,12 @@
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
         <v>1</v>
       </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -720,11 +703,11 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>030ABC</t>
+          <t>036C</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -732,39 +715,36 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>11.8872</v>
+        <v>10.668</v>
       </c>
       <c r="F6" t="n">
-        <v>9.18</v>
+        <v>7.46</v>
       </c>
       <c r="G6" t="n">
-        <v>16.66</v>
+        <v>19.03</v>
       </c>
       <c r="H6" t="n">
-        <v>0.918918918918919</v>
+        <v>1.741935483870968</v>
       </c>
       <c r="I6" t="n">
-        <v>1.81</v>
+        <v>2.18</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.9375</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0.0625</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.9375</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="inlineStr">
+        <v>0.875</v>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -773,7 +753,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>035C</t>
+          <t>058C</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -785,39 +765,36 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>12.4968</v>
+        <v>8.077200000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>7.39</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>18.99</v>
+        <v>16.27</v>
       </c>
       <c r="H7" t="n">
-        <v>-1</v>
+        <v>1.545454545454545</v>
       </c>
       <c r="I7" t="n">
-        <v>3.99</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>0.9375</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0.0625</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.9375</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="inlineStr">
+        <v>0.875</v>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -826,11 +803,11 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>036C</t>
+          <t>060B</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -838,39 +815,36 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>10.668</v>
+        <v>7.9248</v>
       </c>
       <c r="F8" t="n">
-        <v>7.46</v>
+        <v>9</v>
       </c>
       <c r="G8" t="n">
-        <v>19.03</v>
+        <v>16</v>
       </c>
       <c r="H8" t="n">
-        <v>1.741935483870968</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="I8" t="n">
-        <v>2.18</v>
+        <v>0.88</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O8" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -879,11 +853,11 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>058C</t>
+          <t>068B</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -891,39 +865,36 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>8.077200000000001</v>
+        <v>6.7056</v>
       </c>
       <c r="F9" t="n">
-        <v>9.539999999999999</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>16.27</v>
+        <v>20.8</v>
       </c>
       <c r="H9" t="n">
-        <v>1.545454545454545</v>
+        <v>1.458333333333333</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.13</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.9375</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0.0625</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.9375</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="inlineStr">
+        <v>0.875</v>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -932,7 +903,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>060B</t>
+          <t>071B</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -947,19 +918,19 @@
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>7.9248</v>
+        <v>10.0584</v>
       </c>
       <c r="F10" t="n">
-        <v>9</v>
+        <v>9.57</v>
       </c>
       <c r="G10" t="n">
-        <v>16</v>
+        <v>21.05</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2142857142857143</v>
+        <v>-0.1875</v>
       </c>
       <c r="I10" t="n">
-        <v>0.88</v>
+        <v>1.25</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -968,15 +939,12 @@
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
         <v>1</v>
       </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -985,11 +953,11 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>064B</t>
+          <t>094C</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -997,39 +965,36 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>1.524</v>
+        <v>5.486400000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>10.31</v>
+        <v>14</v>
       </c>
       <c r="G11" t="n">
-        <v>21.97</v>
+        <v>14.2</v>
       </c>
       <c r="H11" t="n">
-        <v>1.787878787878788</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="I11" t="n">
-        <v>7.11</v>
+        <v>1.53</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O11" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -1038,11 +1003,11 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>066A</t>
+          <t>125A</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1050,39 +1015,36 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>1.3716</v>
+        <v>7.9248</v>
       </c>
       <c r="F12" t="n">
-        <v>10.76</v>
+        <v>9.77</v>
       </c>
       <c r="G12" t="n">
-        <v>22.46</v>
+        <v>16.43</v>
       </c>
       <c r="H12" t="n">
-        <v>1.769230769230769</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>3.61</v>
+        <v>1.16</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O12" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -1091,11 +1053,11 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>068B</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1103,39 +1065,36 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>6.7056</v>
+        <v>4.6</v>
       </c>
       <c r="F13" t="n">
-        <v>9.359999999999999</v>
+        <v>10.03</v>
       </c>
       <c r="G13" t="n">
-        <v>20.8</v>
+        <v>20.77</v>
       </c>
       <c r="H13" t="n">
-        <v>1.458333333333333</v>
+        <v>1.433404487688642</v>
       </c>
       <c r="I13" t="n">
-        <v>2.13</v>
+        <v>0.41342143147169</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.9375</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.0625</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5</v>
+        <v>0.9375</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="O13" t="inlineStr">
+        <v>0.875</v>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -1144,11 +1103,11 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>071B</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1156,39 +1115,36 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>10.0584</v>
+        <v>1.5</v>
       </c>
       <c r="F14" t="n">
-        <v>9.57</v>
+        <v>10.12</v>
       </c>
       <c r="G14" t="n">
-        <v>21.05</v>
+        <v>19.12</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.1875</v>
+        <v>1.541641360461585</v>
       </c>
       <c r="I14" t="n">
-        <v>1.25</v>
+        <v>1.08693561108866</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>0.9375</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0.0625</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>0.9375</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="inlineStr">
+        <v>0.875</v>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -1197,7 +1153,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>073C</t>
+          <t>S22</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1209,39 +1165,36 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>7.62</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>9.609999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="G15" t="n">
-        <v>20.68</v>
+        <v>19.35</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5217391304347826</v>
+        <v>1.086738836265223</v>
       </c>
       <c r="I15" t="n">
-        <v>1.12</v>
+        <v>0.806961722029484</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.9375</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.0625</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5</v>
+        <v>0.9375</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="O15" t="inlineStr">
+        <v>0.875</v>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -1250,11 +1203,11 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>094C</t>
+          <t>S23</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1262,39 +1215,36 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>5.486400000000001</v>
+        <v>1.8</v>
       </c>
       <c r="F16" t="n">
-        <v>14</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>14.2</v>
+        <v>19.2</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5882352941176471</v>
+        <v>1.698140741541455</v>
       </c>
       <c r="I16" t="n">
-        <v>1.53</v>
+        <v>2.16766115621638</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.9375</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.0625</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5</v>
+        <v>0.9375</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="O16" t="inlineStr">
+        <v>0.875</v>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -1303,11 +1253,11 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>125A</t>
+          <t>S25</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1315,39 +1265,36 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>7.9248</v>
+        <v>2.1</v>
       </c>
       <c r="F17" t="n">
-        <v>9.77</v>
+        <v>10.12</v>
       </c>
       <c r="G17" t="n">
-        <v>16.43</v>
+        <v>17.91</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>1.699273096764108</v>
       </c>
       <c r="I17" t="n">
-        <v>1.16</v>
+        <v>1.05926908510679</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.9375</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0.0625</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.9375</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="inlineStr">
+        <v>0.875</v>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -1356,7 +1303,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>139B</t>
+          <t>S36</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1368,39 +1315,36 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3716</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>9.699999999999999</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>20.5</v>
+        <v>20.85</v>
       </c>
       <c r="H18" t="n">
-        <v>1.16</v>
+        <v>1.703073214823742</v>
       </c>
       <c r="I18" t="n">
-        <v>1.82</v>
+        <v>1.52091254752852</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.9375</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.0625</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5</v>
+        <v>0.9375</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="O18" t="inlineStr">
+        <v>0.875</v>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -1409,11 +1353,11 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>GL1</t>
+          <t>S37</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1421,39 +1365,36 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>8.039999999999999</v>
+        <v>9.99</v>
       </c>
       <c r="G19" t="n">
-        <v>26.89</v>
+        <v>20.31</v>
       </c>
       <c r="H19" t="n">
-        <v>1.611842946668372</v>
+        <v>1.560624659028914</v>
       </c>
       <c r="I19" t="n">
-        <v>1.07</v>
+        <v>1.21254379102751</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1</v>
+        <v>0.9375</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>0.0625</v>
       </c>
       <c r="L19" t="n">
-        <v>0.9</v>
+        <v>0.9375</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O19" t="inlineStr">
+        <v>0.875</v>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -1462,7 +1403,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>S38</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1474,39 +1415,36 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>6</v>
+        <v>0.8</v>
       </c>
       <c r="F20" t="n">
-        <v>10</v>
+        <v>10.03</v>
       </c>
       <c r="G20" t="n">
-        <v>18.02</v>
+        <v>20.01</v>
       </c>
       <c r="H20" t="n">
-        <v>1.162022194821208</v>
+        <v>1.54444673610395</v>
       </c>
       <c r="I20" t="n">
-        <v>1.71138107667851</v>
+        <v>0.541078316722817</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.9375</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.0625</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5</v>
+        <v>0.9375</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="O20" t="inlineStr">
+        <v>0.875</v>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -1515,11 +1453,11 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>S39</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1527,39 +1465,36 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" t="n">
-        <v>10.2</v>
+        <v>9.17</v>
       </c>
       <c r="G21" t="n">
-        <v>19.35</v>
+        <v>20.96</v>
       </c>
       <c r="H21" t="n">
-        <v>1.086738836265223</v>
+        <v>1.604751287768125</v>
       </c>
       <c r="I21" t="n">
-        <v>0.806961722029484</v>
+        <v>0.850441042680259</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.9375</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.0625</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5</v>
+        <v>0.9375</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="O21" t="inlineStr">
+        <v>0.875</v>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -1568,7 +1503,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>S28</t>
+          <t>S50</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1580,39 +1515,36 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="F22" t="n">
-        <v>9.699999999999999</v>
+        <v>9.85</v>
       </c>
       <c r="G22" t="n">
-        <v>15.8</v>
+        <v>20.73</v>
       </c>
       <c r="H22" t="n">
-        <v>1.542817329617431</v>
+        <v>1.589033942558747</v>
       </c>
       <c r="I22" t="n">
-        <v>1.84203344898835</v>
+        <v>2.14788592339205</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.9375</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.0625</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5</v>
+        <v>0.9375</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="O22" t="inlineStr">
+        <v>0.875</v>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -1621,11 +1553,11 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>S28(5)</t>
+          <t>S65</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1633,39 +1565,36 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="F23" t="n">
-        <v>7</v>
+        <v>9.68</v>
       </c>
       <c r="G23" t="n">
-        <v>22.5</v>
+        <v>20.15</v>
       </c>
       <c r="H23" t="n">
-        <v>1.560047918538485</v>
+        <v>1.510708234496781</v>
       </c>
       <c r="I23" t="n">
-        <v>1.53</v>
+        <v>0.67004569366047</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>0.9375</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0.0625</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>0.9375</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
-      </c>
-      <c r="N23" t="n">
-        <v>1</v>
-      </c>
-      <c r="O23" t="inlineStr">
+        <v>0.875</v>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -1674,11 +1603,11 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>S79</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1686,39 +1615,36 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F24" t="n">
-        <v>9.859999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="G24" t="n">
-        <v>20.85</v>
+        <v>19.23</v>
       </c>
       <c r="H24" t="n">
-        <v>1.703073214823742</v>
+        <v>1.114988392338943</v>
       </c>
       <c r="I24" t="n">
-        <v>1.52091254752852</v>
+        <v>1.16723767030516</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1</v>
+        <v>0.9375</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>0.0625</v>
       </c>
       <c r="L24" t="n">
-        <v>0.9</v>
+        <v>0.9375</v>
       </c>
       <c r="M24" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O24" t="inlineStr">
+        <v>0.875</v>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -1727,11 +1653,11 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1739,39 +1665,36 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="F25" t="n">
-        <v>9.99</v>
+        <v>9.77</v>
       </c>
       <c r="G25" t="n">
-        <v>20.31</v>
+        <v>19.85</v>
       </c>
       <c r="H25" t="n">
-        <v>1.560624659028914</v>
+        <v>1.603237791932059</v>
       </c>
       <c r="I25" t="n">
-        <v>1.21254379102751</v>
+        <v>1.00433351312142</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1</v>
+        <v>0.9375</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>0.0625</v>
       </c>
       <c r="L25" t="n">
-        <v>0.9</v>
+        <v>0.9375</v>
       </c>
       <c r="M25" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O25" t="inlineStr">
+        <v>0.875</v>
+      </c>
+      <c r="N25" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -1780,11 +1703,11 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>S81</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1792,569 +1715,36 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="F26" t="n">
-        <v>10.03</v>
+        <v>9.16</v>
       </c>
       <c r="G26" t="n">
-        <v>20.01</v>
+        <v>18.84</v>
       </c>
       <c r="H26" t="n">
-        <v>1.54444673610395</v>
+        <v>-1.079185835773038</v>
       </c>
       <c r="I26" t="n">
-        <v>0.541078316722817</v>
+        <v>0.942177344013984</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3571428571428572</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>0.1428571428571428</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Train</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>S39</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>3</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>3</v>
-      </c>
-      <c r="E27" t="n">
-        <v>2</v>
-      </c>
-      <c r="F27" t="n">
-        <v>9.17</v>
-      </c>
-      <c r="G27" t="n">
-        <v>20.96</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1.604751287768125</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.850441042680259</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>Train</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>S50</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>3</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>3</v>
-      </c>
-      <c r="E28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="F28" t="n">
-        <v>9.85</v>
-      </c>
-      <c r="G28" t="n">
-        <v>20.73</v>
-      </c>
-      <c r="H28" t="n">
-        <v>1.589033942558747</v>
-      </c>
-      <c r="I28" t="n">
-        <v>2.14788592339205</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>Train</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>S52</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>2</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>3</v>
-      </c>
-      <c r="E29" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="F29" t="n">
-        <v>9.449999999999999</v>
-      </c>
-      <c r="G29" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="H29" t="n">
-        <v>1.473299221677717</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.758892017654233</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.3571428571428572</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>Train</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>S54</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>2</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>2</v>
-      </c>
-      <c r="E30" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="F30" t="n">
-        <v>8.91</v>
-      </c>
-      <c r="G30" t="n">
-        <v>21.15</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1.520124887150165</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.601560297020399</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1</v>
-      </c>
-      <c r="N30" t="n">
-        <v>1</v>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>Train</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>S65</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>3</v>
-      </c>
-      <c r="E31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F31" t="n">
-        <v>9.68</v>
-      </c>
-      <c r="G31" t="n">
-        <v>20.15</v>
-      </c>
-      <c r="H31" t="n">
-        <v>1.510708234496781</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.67004569366047</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0.3571428571428572</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>Train</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>S70</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>3</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>3</v>
-      </c>
-      <c r="E32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F32" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="G32" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1.310133297964056</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0.719020334793854</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0.3571428571428572</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>Train</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>S72</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>2</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>2</v>
-      </c>
-      <c r="E33" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="F33" t="n">
-        <v>10.98</v>
-      </c>
-      <c r="G33" t="n">
-        <v>21.84</v>
-      </c>
-      <c r="H33" t="n">
-        <v>1.3034886557697</v>
-      </c>
-      <c r="I33" t="n">
-        <v>1.07155989004254</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>1</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1</v>
-      </c>
-      <c r="N33" t="n">
-        <v>1</v>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>Train</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>S79</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>3</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>3</v>
-      </c>
-      <c r="E34" t="n">
-        <v>4</v>
-      </c>
-      <c r="F34" t="n">
-        <v>9.33</v>
-      </c>
-      <c r="G34" t="n">
-        <v>19.23</v>
-      </c>
-      <c r="H34" t="n">
-        <v>1.114988392338943</v>
-      </c>
-      <c r="I34" t="n">
-        <v>1.16723767030516</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0.3571428571428572</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>Train</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>S8</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>3</v>
-      </c>
-      <c r="E35" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="F35" t="n">
-        <v>9.77</v>
-      </c>
-      <c r="G35" t="n">
-        <v>19.85</v>
-      </c>
-      <c r="H35" t="n">
-        <v>1.603237791932059</v>
-      </c>
-      <c r="I35" t="n">
-        <v>1.00433351312142</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>Train</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>S81</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>3</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>3</v>
-      </c>
-      <c r="E36" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F36" t="n">
-        <v>9.16</v>
-      </c>
-      <c r="G36" t="n">
-        <v>18.84</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-1.079185835773038</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0.942177344013984</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0.3571428571428572</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="O36" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="N26" t="inlineStr">
         <is>
           <t>Train</t>
         </is>

--- a/results/02_taxa_assemblage/MRT_Method/ModelA_CoreOnly/tables/site_eval_train.xlsx
+++ b/results/02_taxa_assemblage/MRT_Method/ModelA_CoreOnly/tables/site_eval_train.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:O43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,15 +486,20 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>Prob_Cluster 3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>p_max</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>delta_p</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
@@ -533,18 +538,21 @@
         <v>0.78</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N2" t="inlineStr">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -565,7 +573,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>3.3528</v>
@@ -583,18 +591,21 @@
         <v>1.43</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N3" t="inlineStr">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -603,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>030ABC</t>
+          <t>026C</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -615,36 +626,39 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>11.8872</v>
+        <v>8.9916</v>
       </c>
       <c r="F4" t="n">
-        <v>9.18</v>
+        <v>6.88</v>
       </c>
       <c r="G4" t="n">
-        <v>16.66</v>
+        <v>19.68</v>
       </c>
       <c r="H4" t="n">
-        <v>0.918918918918919</v>
+        <v>0.3125</v>
       </c>
       <c r="I4" t="n">
-        <v>1.81</v>
+        <v>1.795</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="inlineStr">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -653,7 +667,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>035C</t>
+          <t>030ABC</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -665,36 +679,39 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>12.4968</v>
+        <v>11.8872</v>
       </c>
       <c r="F5" t="n">
-        <v>7.39</v>
+        <v>9.18</v>
       </c>
       <c r="G5" t="n">
-        <v>18.99</v>
+        <v>16.66</v>
       </c>
       <c r="H5" t="n">
-        <v>-1</v>
+        <v>0.918918918918919</v>
       </c>
       <c r="I5" t="n">
-        <v>3.99</v>
+        <v>1.81</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="inlineStr">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -703,7 +720,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>036C</t>
+          <t>033ABC</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -718,33 +735,36 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>10.668</v>
+        <v>9.144</v>
       </c>
       <c r="F6" t="n">
-        <v>7.46</v>
+        <v>6.55</v>
       </c>
       <c r="G6" t="n">
-        <v>19.03</v>
+        <v>19.13</v>
       </c>
       <c r="H6" t="n">
-        <v>1.741935483870968</v>
+        <v>1.1</v>
       </c>
       <c r="I6" t="n">
-        <v>2.18</v>
+        <v>1.45</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9375</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0625</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9375</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="M6" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="N6" t="inlineStr">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -753,7 +773,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>058C</t>
+          <t>035C</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,33 +788,36 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>8.077200000000001</v>
+        <v>12.4968</v>
       </c>
       <c r="F7" t="n">
-        <v>9.539999999999999</v>
+        <v>7.39</v>
       </c>
       <c r="G7" t="n">
-        <v>16.27</v>
+        <v>18.99</v>
       </c>
       <c r="H7" t="n">
-        <v>1.545454545454545</v>
+        <v>-1</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9399999999999999</v>
+        <v>3.99</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9375</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0625</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9375</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="M7" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="N7" t="inlineStr">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -803,11 +826,11 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>060B</t>
+          <t>036C</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -815,36 +838,39 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>7.9248</v>
+        <v>10.668</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>7.46</v>
       </c>
       <c r="G8" t="n">
-        <v>16</v>
+        <v>19.03</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2142857142857143</v>
+        <v>1.741935483870968</v>
       </c>
       <c r="I8" t="n">
-        <v>0.88</v>
+        <v>2.18</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="inlineStr">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -853,11 +879,11 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>068B</t>
+          <t>058C</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -868,33 +894,36 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>6.7056</v>
+        <v>8.077200000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>9.359999999999999</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>20.8</v>
+        <v>16.27</v>
       </c>
       <c r="H9" t="n">
-        <v>1.458333333333333</v>
+        <v>1.545454545454545</v>
       </c>
       <c r="I9" t="n">
-        <v>2.13</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9375</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0625</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="L9" t="n">
-        <v>0.9375</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="M9" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="N9" t="inlineStr">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -903,7 +932,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>071B</t>
+          <t>060B</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -915,36 +944,39 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>10.0584</v>
+        <v>7.9248</v>
       </c>
       <c r="F10" t="n">
-        <v>9.57</v>
+        <v>9</v>
       </c>
       <c r="G10" t="n">
-        <v>21.05</v>
+        <v>16</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1875</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="I10" t="n">
-        <v>1.25</v>
+        <v>0.88</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="inlineStr">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -953,11 +985,11 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>094C</t>
+          <t>064B</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -965,36 +997,39 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>5.486400000000001</v>
+        <v>1.524</v>
       </c>
       <c r="F11" t="n">
-        <v>14</v>
+        <v>10.31</v>
       </c>
       <c r="G11" t="n">
-        <v>14.2</v>
+        <v>21.97</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5882352941176471</v>
+        <v>1.787878787878788</v>
       </c>
       <c r="I11" t="n">
-        <v>1.53</v>
+        <v>7.11</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="inlineStr">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -1003,11 +1038,11 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>125A</t>
+          <t>068B</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1015,36 +1050,39 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>7.9248</v>
+        <v>6.7056</v>
       </c>
       <c r="F12" t="n">
-        <v>9.77</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>16.43</v>
+        <v>20.8</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>1.458333333333333</v>
       </c>
       <c r="I12" t="n">
-        <v>1.16</v>
+        <v>2.13</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="inlineStr">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="O12" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -1053,11 +1091,11 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>071B</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1068,33 +1106,36 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>4.6</v>
+        <v>10.0584</v>
       </c>
       <c r="F13" t="n">
-        <v>10.03</v>
+        <v>9.57</v>
       </c>
       <c r="G13" t="n">
-        <v>20.77</v>
+        <v>21.05</v>
       </c>
       <c r="H13" t="n">
-        <v>1.433404487688642</v>
+        <v>-0.1875</v>
       </c>
       <c r="I13" t="n">
-        <v>0.41342143147169</v>
+        <v>1.25</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9375</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0625</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="L13" t="n">
-        <v>0.9375</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="M13" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="N13" t="inlineStr">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="O13" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -1103,7 +1144,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>073C</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1118,33 +1159,36 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5</v>
+        <v>7.62</v>
       </c>
       <c r="F14" t="n">
-        <v>10.12</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>19.12</v>
+        <v>20.68</v>
       </c>
       <c r="H14" t="n">
-        <v>1.541641360461585</v>
+        <v>0.5217391304347826</v>
       </c>
       <c r="I14" t="n">
-        <v>1.08693561108866</v>
+        <v>1.12</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9375</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0625</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="L14" t="n">
-        <v>0.9375</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="M14" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="N14" t="inlineStr">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -1153,11 +1197,11 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>094C</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1168,33 +1212,36 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>5.486400000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>10.2</v>
+        <v>14</v>
       </c>
       <c r="G15" t="n">
-        <v>19.35</v>
+        <v>14.2</v>
       </c>
       <c r="H15" t="n">
-        <v>1.086738836265223</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="I15" t="n">
-        <v>0.806961722029484</v>
+        <v>1.53</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9375</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0625</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="L15" t="n">
-        <v>0.9375</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="M15" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="N15" t="inlineStr">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -1203,11 +1250,11 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>109C</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1218,33 +1265,36 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8</v>
+        <v>3.048</v>
       </c>
       <c r="F16" t="n">
-        <v>9.789999999999999</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>19.2</v>
+        <v>19.5</v>
       </c>
       <c r="H16" t="n">
-        <v>1.698140741541455</v>
+        <v>1.05</v>
       </c>
       <c r="I16" t="n">
-        <v>2.16766115621638</v>
+        <v>1.1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9375</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0625</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="L16" t="n">
-        <v>0.9375</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="M16" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="N16" t="inlineStr">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -1253,11 +1303,11 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>125A</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1268,33 +1318,36 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1</v>
+        <v>7.9248</v>
       </c>
       <c r="F17" t="n">
-        <v>10.12</v>
+        <v>9.77</v>
       </c>
       <c r="G17" t="n">
-        <v>17.91</v>
+        <v>16.43</v>
       </c>
       <c r="H17" t="n">
-        <v>1.699273096764108</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>1.05926908510679</v>
+        <v>1.16</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9375</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0625</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="L17" t="n">
-        <v>0.9375</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="M17" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="N17" t="inlineStr">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="O17" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -1303,11 +1356,11 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>133B</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1318,33 +1371,36 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>1.8288</v>
       </c>
       <c r="F18" t="n">
-        <v>9.859999999999999</v>
+        <v>11.76</v>
       </c>
       <c r="G18" t="n">
-        <v>20.85</v>
+        <v>20.62</v>
       </c>
       <c r="H18" t="n">
-        <v>1.703073214823742</v>
+        <v>1.023255813953488</v>
       </c>
       <c r="I18" t="n">
-        <v>1.52091254752852</v>
+        <v>1.55</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9375</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0625</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="L18" t="n">
-        <v>0.9375</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="M18" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="N18" t="inlineStr">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="O18" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -1353,7 +1409,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>139B</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1368,33 +1424,36 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>1.3716</v>
       </c>
       <c r="F19" t="n">
-        <v>9.99</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>20.31</v>
+        <v>20.5</v>
       </c>
       <c r="H19" t="n">
-        <v>1.560624659028914</v>
+        <v>1.16</v>
       </c>
       <c r="I19" t="n">
-        <v>1.21254379102751</v>
+        <v>1.82</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9375</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0625</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="L19" t="n">
-        <v>0.9375</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="M19" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="N19" t="inlineStr">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="O19" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -1403,7 +1462,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1418,33 +1477,36 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8</v>
+        <v>4.6</v>
       </c>
       <c r="F20" t="n">
         <v>10.03</v>
       </c>
       <c r="G20" t="n">
-        <v>20.01</v>
+        <v>20.77</v>
       </c>
       <c r="H20" t="n">
-        <v>1.54444673610395</v>
+        <v>1.433404487688642</v>
       </c>
       <c r="I20" t="n">
-        <v>0.541078316722817</v>
+        <v>0.41342143147169</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9375</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0625</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="L20" t="n">
-        <v>0.9375</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="M20" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="N20" t="inlineStr">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="O20" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -1453,7 +1515,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1468,33 +1530,36 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="F21" t="n">
-        <v>9.17</v>
+        <v>10.12</v>
       </c>
       <c r="G21" t="n">
-        <v>20.96</v>
+        <v>19.12</v>
       </c>
       <c r="H21" t="n">
-        <v>1.604751287768125</v>
+        <v>1.541641360461585</v>
       </c>
       <c r="I21" t="n">
-        <v>0.850441042680259</v>
+        <v>1.08693561108866</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9375</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0625</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="L21" t="n">
-        <v>0.9375</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="M21" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="N21" t="inlineStr">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="O21" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -1503,7 +1568,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>S50</t>
+          <t>S18</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1518,33 +1583,36 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="F22" t="n">
-        <v>9.85</v>
+        <v>10.4</v>
       </c>
       <c r="G22" t="n">
-        <v>20.73</v>
+        <v>19.57</v>
       </c>
       <c r="H22" t="n">
-        <v>1.589033942558747</v>
+        <v>1.62995516333357</v>
       </c>
       <c r="I22" t="n">
-        <v>2.14788592339205</v>
+        <v>1.50490599353894</v>
       </c>
       <c r="J22" t="n">
-        <v>0.9375</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0625</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="L22" t="n">
-        <v>0.9375</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="M22" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="N22" t="inlineStr">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="O22" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -1553,7 +1621,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>S65</t>
+          <t>S21</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1568,33 +1636,36 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.2</v>
+        <v>6</v>
       </c>
       <c r="F23" t="n">
-        <v>9.68</v>
+        <v>10</v>
       </c>
       <c r="G23" t="n">
-        <v>20.15</v>
+        <v>18.02</v>
       </c>
       <c r="H23" t="n">
-        <v>1.510708234496781</v>
+        <v>1.162022194821208</v>
       </c>
       <c r="I23" t="n">
-        <v>0.67004569366047</v>
+        <v>1.71138107667851</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9375</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0625</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="L23" t="n">
-        <v>0.9375</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="M23" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="N23" t="inlineStr">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="O23" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -1603,7 +1674,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>S79</t>
+          <t>S22</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1618,33 +1689,36 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>9.33</v>
+        <v>10.2</v>
       </c>
       <c r="G24" t="n">
-        <v>19.23</v>
+        <v>19.35</v>
       </c>
       <c r="H24" t="n">
-        <v>1.114988392338943</v>
+        <v>1.086738836265223</v>
       </c>
       <c r="I24" t="n">
-        <v>1.16723767030516</v>
+        <v>0.806961722029484</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9375</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0625</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="L24" t="n">
-        <v>0.9375</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="M24" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="N24" t="inlineStr">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="O24" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -1653,7 +1727,7 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S23</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1668,33 +1742,36 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="F25" t="n">
-        <v>9.77</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>19.85</v>
+        <v>19.2</v>
       </c>
       <c r="H25" t="n">
-        <v>1.603237791932059</v>
+        <v>1.698140741541455</v>
       </c>
       <c r="I25" t="n">
-        <v>1.00433351312142</v>
+        <v>2.16766115621638</v>
       </c>
       <c r="J25" t="n">
-        <v>0.9375</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0625</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="L25" t="n">
-        <v>0.9375</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="M25" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="N25" t="inlineStr">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="O25" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -1703,48 +1780,952 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
+          <t>S25</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="G26" t="n">
+        <v>17.91</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.699273096764108</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.05926908510679</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.2142857142857143</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>S28</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F27" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="G27" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.542817329617431</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.84203344898835</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.2142857142857143</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>S28(5)</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>3</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>7</v>
+      </c>
+      <c r="G28" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.560047918538485</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.2142857142857143</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>S36</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="G29" t="n">
+        <v>20.85</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.703073214823742</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.52091254752852</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.2142857142857143</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>S37</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="G30" t="n">
+        <v>20.31</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.560624659028914</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.21254379102751</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.2142857142857143</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>S38</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F31" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="G31" t="n">
+        <v>20.01</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.54444673610395</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.541078316722817</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.2142857142857143</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>S39</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="G32" t="n">
+        <v>20.96</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.604751287768125</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.850441042680259</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.2142857142857143</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>S50</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F33" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="G33" t="n">
+        <v>20.73</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.589033942558747</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2.14788592339205</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.2142857142857143</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>S52</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F34" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="G34" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.473299221677717</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.758892017654233</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.2142857142857143</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>S53</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F35" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="G35" t="n">
+        <v>22.45</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.525052642945845</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.511201323109319</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.2142857142857143</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>S65</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F36" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="G36" t="n">
+        <v>20.15</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.510708234496781</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.67004569366047</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.2142857142857143</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>S69</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>3</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F37" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="G37" t="n">
+        <v>22.89</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.860779140152104</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.84144213994961</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.2142857142857143</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>S70</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>3</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F38" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="G38" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1.310133297964056</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.719020334793854</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.2142857142857143</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>S72</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>3</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F39" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="G39" t="n">
+        <v>21.84</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1.3034886557697</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.07155989004254</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.2142857142857143</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>S74</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>3</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="F40" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="G40" t="n">
+        <v>20.65</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1.652212487523566</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.50636152676643</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.2142857142857143</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>S79</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="n">
+        <v>4</v>
+      </c>
+      <c r="F41" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="G41" t="n">
+        <v>19.23</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1.114988392338943</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.16723767030516</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.2142857142857143</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F42" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="G42" t="n">
+        <v>19.85</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1.603237791932059</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.00433351312142</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.2142857142857143</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
           <t>S81</t>
         </is>
       </c>
-      <c r="B26" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" t="n">
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
         <v>1.8</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F43" t="n">
         <v>9.16</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G43" t="n">
         <v>18.84</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H43" t="n">
         <v>-1.079185835773038</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I43" t="n">
         <v>0.942177344013984</v>
       </c>
-      <c r="J26" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1</v>
-      </c>
-      <c r="N26" t="inlineStr">
+      <c r="J43" t="n">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.2142857142857143</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="O43" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
